--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -37,13 +37,13 @@
     <t xml:space="preserve">destinatario_direccion</t>
   </si>
   <si>
-    <t xml:space="preserve">ciudad</t>
-  </si>
-  <si>
     <t xml:space="preserve">destinatario_telefono</t>
   </si>
   <si>
     <t xml:space="preserve">destinatario_correo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unidades</t>
   </si>
   <si>
     <t xml:space="preserve">peso</t>
@@ -353,10 +353,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.39"/>
   </cols>
   <sheetData>
@@ -421,10 +420,10 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="n">
         <v>3201457478</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
@@ -444,8 +443,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -19,6 +19,235 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Número de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Fecha de registro de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Número interno de la guia o visita del cliente </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Nombre del destinatario de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dirección exacta de la visita, debe tener la estructura del empleado: </t>
+        </r>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dirección. Barrio, Ciudad</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Número de teléfono de contacto del destinatario puede ser fijo o celular.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Unidades del producto de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Peso total en KG del total de la guia o visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Volumen total de la guia o visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tiempo del servicio en minutos de la visita o guia.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
@@ -77,7 +306,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -99,6 +328,17 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -109,8 +349,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6D6D"/>
-        <bgColor rgb="FFFF6600"/>
+        <fgColor rgb="FFFFFF38"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,11 +397,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -181,7 +421,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFFF38"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -197,7 +437,7 @@
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF6D6D"/>
+      <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
@@ -366,40 +606,40 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -425,7 +665,7 @@
       <c r="H2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="n">
@@ -446,5 +686,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -29,113 +29,114 @@
       <text>
         <r>
           <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Número de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve"> Fecha de registro de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Número interno de la guia o visita del cliente </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve"> Nombre del destinatario de la visita</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Dirección exacta de la visita, debe tener la estructura del empleado: </t>
+        </r>
+        <r>
+          <rPr>
             <b val="true"/>
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Número de la visita</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> Fecha de registro de la visita</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Número interno de la guia o visita del cliente </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> Nombre del destinatario de la visita</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Dirección exacta de la visita, debe tener la estructura del empleado: </t>
-        </r>
-        <r>
-          <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Dirección. Barrio, Ciudad</t>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Dirección, Ciudad, Departamento</t>
         </r>
       </text>
     </comment>
@@ -143,18 +144,18 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Número de teléfono de contacto del destinatario puede ser fijo o celular.</t>
         </r>
@@ -164,18 +165,18 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Unidades del producto de la visita</t>
         </r>
@@ -185,18 +186,18 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Peso total en KG del total de la guia o visita</t>
         </r>
@@ -206,18 +207,18 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Volumen total de la guia o visita</t>
         </r>
@@ -227,18 +228,18 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Obligatorio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obligatorio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Tiempo del servicio en minutos de la visita o guia.</t>
         </r>
@@ -296,7 +297,7 @@
     <t xml:space="preserve">MARCO SANCHEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">CR 40 65AA - 22 B. Villa Hermosa, MEDELLIN</t>
+    <t xml:space="preserve">Cra. 74 #No 48-37, Medellín, Antioquia</t>
   </si>
 </sst>
 </file>
@@ -329,15 +330,16 @@
       <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -592,7 +594,7 @@
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="61.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12.1"/>

--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -126,7 +126,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Dirección exacta de la visita, debe tener la estructura del empleado: </t>
+          <t xml:space="preserve">Dirección exacta de la visita, debe tener la siguiente estructura: </t>
         </r>
         <r>
           <rPr>

--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -1,52 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -64,14 +44,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,103 +444,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>numero</v>
-      </c>
-      <c r="B1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="C1" t="str">
-        <v>documento</v>
-      </c>
-      <c r="D1" t="str">
-        <v>destinatario</v>
-      </c>
-      <c r="E1" t="str">
-        <v>destinatario_direccion</v>
-      </c>
-      <c r="F1" t="str">
-        <v>destinatario_telefono</v>
-      </c>
-      <c r="G1" t="str">
-        <v>destinatario_correo</v>
-      </c>
-      <c r="H1" t="str">
-        <v>unidades</v>
-      </c>
-      <c r="I1" t="str">
-        <v>peso</v>
-      </c>
-      <c r="J1" t="str">
-        <v>volumen</v>
-      </c>
-      <c r="K1" t="str">
-        <v>latitud</v>
-      </c>
-      <c r="L1" t="str">
-        <v>longitud</v>
-      </c>
-      <c r="M1" t="str">
-        <v>decodificado</v>
-      </c>
-      <c r="N1" t="str">
-        <v>tiempo_servicio</v>
-      </c>
-      <c r="O1" t="str">
-        <v>cita_inicio</v>
-      </c>
-      <c r="P1" t="str">
-        <v>cita_fin</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>numero</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>documento</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>destinatario</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>destinatario_direccion</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>destinatario_telefono</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>destinatario_correo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>unidades</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>peso</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>volumen</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>latitud</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>longitud</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>decodificado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tiempo_servicio</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>cita_inicio</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>cita_fin</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>destinatario_direccion_complemento</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>observacion</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ciudad</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>123456</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>20241001</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>11111</v>
       </c>
-      <c r="D2" t="str">
-        <v>MARCO SANCHEZ</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Cra. 74 #No 48-37, Medellín, Antioquia</v>
-      </c>
-      <c r="F2">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MARCO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cra. 74 #No 48-37</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>3201457478</v>
       </c>
-      <c r="H2">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cliente@correo.com</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>10</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="str">
-        <v>2024-10-01 08:00:00</v>
-      </c>
-      <c r="P2" t="str">
-        <v>2024-10-01 12:00:00</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-10-01 08:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2024-10-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Apto 301</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Entregar antes 12pm</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Medellin</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,11 @@
           <t>ciudad</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>recaudo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -616,6 +621,9 @@
         <is>
           <t>Medellin</t>
         </is>
+      </c>
+      <c r="T2" t="n">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +553,11 @@
           <t>recaudo</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>tarifa</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -624,6 +629,9 @@
       </c>
       <c r="T2" t="n">
         <v>50000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8500</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/ejemplos/modelo/estructuraVisita.xlsx
+++ b/src/assets/ejemplos/modelo/estructuraVisita.xlsx
@@ -1,38 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Visitas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A6A6A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECECEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,18 +101,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -198,7 +300,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,7 +334,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,16 +368,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -399,46 +503,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -449,192 +514,774 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>numero</t>
+          <t>Número *</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>Fecha (YYYYMMDD) *</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>documento</t>
+          <t>Documento *</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>destinatario</t>
+          <t>Destinatario *</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>destinatario_direccion</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>destinatario_telefono</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>destinatario_correo</t>
+          <t>Dirección *</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Teléfono</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Correo</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>unidades</t>
+          <t>Unidades *</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>peso</t>
+          <t>Peso (kg) *</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>volumen</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>latitud</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>longitud</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>decodificado</t>
+          <t>Volumen (m³) *</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>— No usar —</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>— No usar —</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>— No usar —</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>tiempo_servicio</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>cita_inicio</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>cita_fin</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>destinatario_direccion_complemento</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>observacion</t>
+          <t>Tiempo servicio (min) *</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Cita inicio</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Cita fin</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Complemento dirección</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Observación</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>ciudad</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>recaudo</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>tarifa</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>123456</v>
-      </c>
-      <c r="B2" t="n">
-        <v>20241001</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11111</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MARCO SANCHEZ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Cra. 74 #No 48-37</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3201457478</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>cliente@correo.com</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+          <t>Ciudad *</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Cobro</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Tarifa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>GUIA-001</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Otto Hernandez</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Carrera 43A #1-50, El Poblado, Medellín</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>3006134088</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>otto@example.com</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>Apto 301</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>Llamar al llegar</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>GUIA-002</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Cliente Dos</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Calle 10 #38-20, Manila, Medellín</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>3209999999</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>20260507</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>GUIA-003</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Cliente Tres</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Calle 50 #51-15, La Candelaria, Medellín</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>3104444444</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2024-10-01 08:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2024-10-01 12:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Apto 301</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Entregar antes 12pm</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Medellin</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:00:00</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-07 12:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Entregar antes de 12 pm</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="U2" t="n">
-        <v>8500</v>
+      <c r="U4" s="4" t="n">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="7">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Teléfono inválido" error="Debe tener entre 7 y 15 caracteres (idealmente 10 dígitos para celular CO)." type="textLength" operator="between">
+      <formula1>7</formula1>
+      <formula2>15</formula2>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Debe ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Debe ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Debe ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Debe ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Debe ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Debe ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Importar visitas — Plantilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Cargá esta plantilla en Visitas → Importar Excel. Cada fila se convierte en una visita decodificada por Google Maps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Reglas generales</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>• Cabecera</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>La fila 1 son los nombres de columna. NO la elimines ni cambies su orden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>• Datos</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Llenar desde la fila 2 en adelante. Borrar las 3 filas de ejemplo antes de subir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>• Máximo</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Hasta el límite configurado en el tenant (rut_limite_importacion, default 500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>• Atómico</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Si UNA sola fila tiene error, NO se importa ninguna. Corregí el Excel y volvé a subir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Códigos de color</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>🟦 Azul oscuro</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Campo OBLIGATORIO. Si va vacío, la fila falla la validación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>🟦 Azul medio</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Campo OPCIONAL. Podés dejarlo vacío.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>⬜ Gris</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Columnas IGNORADAS por el sistema. Existen para conservar la posición de las demás. NO escribas en ellas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Formato de cada campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Entero. Tu número interno de visita / pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Texto en formato YYYYMMDD. Ej: 20260506 = 6 de mayo de 2026. NO uses formato fecha de Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Texto. Tu número de guía o factura. Máx 30 caracteres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Destinatario</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Nombre de quien recibe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Dirección</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Calle/Carrera + número + sector + ciudad. Mientras más completa, mejor decodifica Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Teléfono</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Celular CO de 10 dígitos (ej. 3006134088). Recibirá WhatsApp al aprobar el despacho si el tenant tiene WhatsApp habilitado. Acepta espacios, +, -.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Opcional. Email del destinatario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Cantidad. Mínimo 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Peso</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Kilogramos. Acepta decimales (ej. 1.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Metros cúbicos. Acepta decimales (ej. 0.05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Tiempo servicio</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Minutos estimados de entrega en sitio (sin contar trayecto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Cita inicio/fin</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Opcional. Texto YYYY-MM-DD HH:MM:SS. Ambos o ninguno, mismo día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Complemento dir</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Opcional. Apto, oficina, torre, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Opcional. Notas para el conductor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Ciudad</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Nombre exacto de la ciudad. CON tilde si la tiene (ej. "Medellín", no "Medellin"). Si no matchea queda sin ciudad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Cobro</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Valor a recaudar al entregar (COP). 0 si no aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Tarifa</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Costo del servicio (COP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Qué pasa al subir</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>1. Validación</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Cada fila se valida contra el modelo. Si hay errores, response trae {fila, errores} y NO importa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2. Decodificación</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Cada dirección se manda a Google Maps. Tarda ~1s por fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>3. Asignación de franja</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Si la dirección queda dentro de una franja geográfica, se le asigna automáticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>4. Reordenamiento</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Al final, todas las visitas pendientes (sin despacho) se reubican y se reordenan.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A35:B35"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>